--- a/data/trans_camb/IMC_inf_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-3.664786014799243</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.814946908954177</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-7.443205263827396</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-12.99417352553442</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-5.443135207895411</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-9.07318056142784</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-11.95772781623721</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.30292798580684</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-15.64512544488014</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-23.90269413138538</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-11.37485903128361</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-17.12829627822531</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>5.285389281506539</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.695034252988874</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.2594736738700295</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.6992111565381962</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5060550537205343</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.508369058211824</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.07128248324691482</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1131045179569459</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.1610278504729288</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2811186521561942</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.111394155238038</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1856832956301353</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.2139605397362108</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.3318346676774993</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3135578867788247</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4904091208895738</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2190337878216332</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3382184911514281</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1112605604036951</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1169191309860843</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.01052924036114708</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.01970608410477804</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01151807652537952</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.01040082614357343</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-10.03326037091988</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-11.31030473247535</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-6.523283553935705</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-11.90622265954426</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-8.327887228412834</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-11.38423428518839</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-18.82036053149124</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-21.45703264577281</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-16.24041252757411</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-20.00221401791069</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-14.10802157037304</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-17.39010016688272</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>-0.8121149510225699</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.966517635524356</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.103335362754209</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-3.040408212072674</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-2.198598055444159</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-4.198926590139553</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.1969269712732255</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.2219920517162252</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1675992836512042</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3059002988651965</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1847030683280571</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2524893703970705</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3473092492961504</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.3899916008648979</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3594775920289932</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.4731581610032733</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2952918882345604</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3695480356105204</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>-0.01811470864356383</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.01723374622107332</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.06657857034712625</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.0908247301020519</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.04806266257857467</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.1049150118816835</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-5.437608355478734</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-9.773518141349957</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-7.019585659563998</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-10.5783765180332</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-6.321097482922439</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-9.762349438528567</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-16.35808395076613</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-19.04497489694611</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-17.02624741310566</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-20.25652900947071</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-13.19576360451195</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-16.16550839860735</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.522301729686304</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.007112327854073267</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.483164238669614</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-2.002147174471605</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.218154604268126</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-2.880982079962447</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.1094403230394737</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1967072493449788</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.1741857126408133</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.2624944180096958</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1401201868498508</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2164026470270057</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.299335049974957</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.3535402948861937</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.385677985305433</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.4406693270736716</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.279030863282734</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3327038208013207</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.1003012424286169</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.001248041243979746</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.09762029544548684</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.05936644651767481</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.03069098919045715</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.07373077350111167</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.4111888022591381</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-12.94286203511691</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-10.54018192505643</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-15.68463955419455</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-4.631064575147298</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-14.44624150870384</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-14.77160679991624</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-25.80303537574607</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-26.01033929273624</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-28.37523536409068</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-14.34848634451308</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-23.95476007558924</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>12.33452396348973</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.33760246870686</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.097331559700414</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-3.43938563155136</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>5.681426707639925</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-5.468777546354318</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.008952835363879742</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2818056141149112</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.2511904935182535</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3737916838900249</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1050830277547118</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3277982357570802</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.2811088002772931</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.4888519352265133</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.5319875886544131</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5620293382828362</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.294015707957141</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.4751191236502404</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.311859277975859</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.03945345647465604</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.09846888617663833</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.08065043368469563</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.1546431211697607</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.1455636687735022</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-5.436116332983953</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-11.04146923519762</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-7.207945101152924</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-13.56879252024485</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-6.249840983964622</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-12.092037002198</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-10.06933340609602</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-16.77638989405884</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-12.76150366328985</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-18.84947920918135</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-9.7947749473963</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-16.06203829028019</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.5497087969664185</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-5.924334207922423</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-2.739767067447767</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-8.909789378822833</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-2.849403431639709</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-8.50737451045708</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1083087186496202</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.219989292285255</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1712108259641225</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.3223004812224972</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1351133300321689</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.2614139128389103</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.1898500303929767</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.3174553490077507</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2867515592833527</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.4210035165813858</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2024748153804855</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3321190777647089</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.01108006273722834</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.1227973102675347</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.06938918206976928</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.2217939548517605</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.06275855795423098</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.1893353117798998</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
